--- a/rosters/player_roles_hitters_2027.xlsx
+++ b/rosters/player_roles_hitters_2027.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -757,26 +757,71 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>CALIBRATION STATUS:</t>
+          <t>THE PROJECTION COLUMNS:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Every anchor on the Roles sheet is a documented starting point, not a fitted value. Fit them</t>
+          <t xml:space="preserve">  Proj PA and the columns beside it are FORMULAS, so they update as you edit probabilities.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  from history (group real player-seasons by observed role) before trusting the levels. The</t>
+          <t xml:space="preserve">  They show blank until you open this file in Excel or LibreOffice, which computes them on</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  open — openpyxl cannot write cached values alongside a formula. That is cosmetic: the</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  pipeline reads the INPUT columns (role probabilities, Role Start, Availability) and recomputes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the volumes itself, so a blank formula cell never reaches a projection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>CALIBRATION STATUS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Every anchor on the Roles sheet is a documented starting point, not a fitted value. Fit them</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  from history (group real player-seasons by observed role) before trusting the levels. The</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  cross-role ORDERING is more reliable than the absolute numbers.</t>
         </is>
